--- a/data/Museum leaderboard.xlsx
+++ b/data/Museum leaderboard.xlsx
@@ -5,22 +5,34 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brinda/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brinda/Documents/MRes project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8831E07B-2510-DF44-92ED-61396C2AFBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041C61F0-E5F6-8C4F-9929-46013C203B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
   <si>
     <t>Source/Collection</t>
   </si>
@@ -34,9 +46,6 @@
     <t>UPLB (University of the Philippines Los Baños)</t>
   </si>
   <si>
-    <t>NHMUK, Tring</t>
-  </si>
-  <si>
     <t>UMMZ (University of Michigan Museum of Zoology)</t>
   </si>
   <si>
@@ -52,9 +61,6 @@
     <t>AMNH (American Museum of Natural History)</t>
   </si>
   <si>
-    <t>NMK, Kenya</t>
-  </si>
-  <si>
     <t>CUMV (Cornell University Museum of Vertebrates)</t>
   </si>
   <si>
@@ -85,18 +91,9 @@
     <t>CNM (Colombo National Museum)</t>
   </si>
   <si>
-    <t>NHNM Philippines (National Museum of Natural History)</t>
-  </si>
-  <si>
     <t>LKCNHM (Lee Kong Chian Natural History Museum), Singapore</t>
   </si>
   <si>
-    <t>MZB (Museum Zoologicum Bogoriense)</t>
-  </si>
-  <si>
-    <t>Naturalis, Leiden</t>
-  </si>
-  <si>
     <t>OUM</t>
   </si>
   <si>
@@ -184,9 +181,6 @@
     <t>IISER Tirupati, India</t>
   </si>
   <si>
-    <t>NMNH Smithsonian</t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
@@ -194,6 +188,27 @@
   </si>
   <si>
     <t>BNHS (Bombay Natural History Society), India</t>
+  </si>
+  <si>
+    <t>UWO (University of Western Ontario)</t>
+  </si>
+  <si>
+    <t>NMK (National Museums Kenya), Kenya</t>
+  </si>
+  <si>
+    <t>NMNH(National Museum of Natural History), Smithsonian</t>
+  </si>
+  <si>
+    <t>NHMUK (Natural History Museum UK), Tring</t>
+  </si>
+  <si>
+    <t>NMNH (National Museum of Natural History), Philippines</t>
+  </si>
+  <si>
+    <t>MZB (Museum Zoologicum Bogoriense), Indonesia</t>
+  </si>
+  <si>
+    <t>RMNH (Naturalis Biodiversity Center), Leiden</t>
   </si>
 </sst>
 </file>
@@ -256,7 +271,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -266,6 +281,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -570,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51" customWidth="1"/>
@@ -590,7 +609,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -609,7 +628,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="B3" s="2">
         <v>1000</v>
@@ -623,7 +642,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2">
         <v>532</v>
@@ -637,7 +656,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
         <v>501</v>
@@ -651,10 +670,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -665,10 +684,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
@@ -679,7 +698,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2">
         <v>492</v>
@@ -693,7 +712,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2">
         <v>490</v>
@@ -707,7 +726,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2">
         <v>357</v>
@@ -724,7 +743,7 @@
         <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C11" s="2">
         <v>0</v>
@@ -735,7 +754,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2">
         <v>236</v>
@@ -749,80 +768,80 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
+      </c>
+      <c r="B13" s="2">
+        <v>217</v>
       </c>
       <c r="C13" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D13" s="2">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C14" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D14" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6">
         <v>138</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="4">
         <v>122</v>
       </c>
-      <c r="C15" s="4">
-        <v>0</v>
-      </c>
-      <c r="D15" s="4">
+      <c r="C16" s="4">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
         <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2">
-        <v>117</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0</v>
-      </c>
-      <c r="D16" s="2">
-        <v>117</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
+      </c>
+      <c r="B17" s="2">
+        <v>117</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2">
         <v>0</v>
@@ -833,10 +852,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2">
         <v>0</v>
@@ -847,10 +866,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -861,7 +880,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B21" s="2">
         <v>84</v>
@@ -875,7 +894,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B22" s="2">
         <v>83</v>
@@ -889,7 +908,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2">
         <v>75</v>
@@ -903,7 +922,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B24" s="2">
         <v>72</v>
@@ -917,10 +936,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C25" s="2">
         <v>0</v>
@@ -931,24 +950,24 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
+      </c>
+      <c r="B26" s="2">
+        <v>54</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
       </c>
       <c r="D26" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C27" s="2">
         <v>0</v>
@@ -959,10 +978,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -973,24 +992,24 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="2">
-        <v>49</v>
+        <v>57</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="C29" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D29" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -1001,7 +1020,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B31" s="2">
         <v>29</v>
@@ -1015,7 +1034,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B32" s="2">
         <v>23</v>
@@ -1029,91 +1048,91 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
       </c>
       <c r="D33" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
       </c>
       <c r="D34" s="2">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="2">
-        <v>19</v>
+        <v>52</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
       </c>
       <c r="D35" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B36" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
       </c>
       <c r="D36" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B37" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
       </c>
       <c r="D37" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B38" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C38" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B39" s="2">
         <v>0</v>
@@ -1127,21 +1146,21 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B40" s="2">
         <v>0</v>
       </c>
       <c r="C40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B41" s="2">
         <v>0</v>
@@ -1155,7 +1174,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B42" s="2">
         <v>0</v>
@@ -1169,21 +1188,21 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B43" s="2">
         <v>0</v>
       </c>
       <c r="C43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D43" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B44" s="2">
         <v>0</v>
@@ -1197,29 +1216,43 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="B45" s="2">
         <v>0</v>
       </c>
       <c r="C45" s="2">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="D45" s="2">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B46" s="2">
         <v>0</v>
       </c>
       <c r="C46" s="2">
+        <v>42</v>
+      </c>
+      <c r="D46" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" s="2">
+        <v>0</v>
+      </c>
+      <c r="C47" s="2">
         <v>83</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D47" s="2">
         <v>83</v>
       </c>
     </row>

--- a/data/Museum leaderboard.xlsx
+++ b/data/Museum leaderboard.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brinda/Documents/MRes project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{041C61F0-E5F6-8C4F-9929-46013C203B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE11C40-0492-DD45-ADFB-D89E3579E890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>Source/Collection</t>
   </si>
@@ -55,9 +55,6 @@
     <t>NSM (National Science Museum), Thailand</t>
   </si>
   <si>
-    <t>SYSU Guangzhou</t>
-  </si>
-  <si>
     <t>AMNH (American Museum of Natural History)</t>
   </si>
   <si>
@@ -70,18 +67,12 @@
     <t>FLMNH (Florida Museum of Natural History)</t>
   </si>
   <si>
-    <t>HMNH (Harvard Museum of Natural History)</t>
-  </si>
-  <si>
     <t>Academy of Natural Sciences Philadelphia (ANSP)</t>
   </si>
   <si>
     <t>UMZC (University Museum of Zoology Cambridge)</t>
   </si>
   <si>
-    <t>ZFMK</t>
-  </si>
-  <si>
     <t>SMNH (Steinhardt Museum of Natural History)</t>
   </si>
   <si>
@@ -94,9 +85,6 @@
     <t>LKCNHM (Lee Kong Chian Natural History Museum), Singapore</t>
   </si>
   <si>
-    <t>OUM</t>
-  </si>
-  <si>
     <t>Dhaka University</t>
   </si>
   <si>
@@ -145,21 +133,9 @@
     <t>500 (P)</t>
   </si>
   <si>
-    <t>300 (P)</t>
-  </si>
-  <si>
-    <t>200 (P)</t>
-  </si>
-  <si>
     <t>138 (P)</t>
   </si>
   <si>
-    <t>100 (P)</t>
-  </si>
-  <si>
-    <t>57 (P)</t>
-  </si>
-  <si>
     <t>50 (P)</t>
   </si>
   <si>
@@ -209,6 +185,18 @@
   </si>
   <si>
     <t>RMNH (Naturalis Biodiversity Center), Leiden</t>
+  </si>
+  <si>
+    <t>68 (P)</t>
+  </si>
+  <si>
+    <t>SYSU (Sun-Yat-Sen University), Guangzhou</t>
+  </si>
+  <si>
+    <t>ZFMK (Museum Koenig Bonn), Germany</t>
+  </si>
+  <si>
+    <t>OUM (Oxford University Museum of Natural History)</t>
   </si>
 </sst>
 </file>
@@ -271,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -281,10 +269,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -589,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51" customWidth="1"/>
@@ -609,35 +593,35 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="B2" s="2">
-        <v>1183</v>
+        <v>1000</v>
       </c>
       <c r="C2" s="2">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="D2" s="2">
-        <v>1183</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>1000</v>
+        <v>1049</v>
       </c>
       <c r="C3" s="2">
-        <v>636</v>
+        <v>0</v>
       </c>
       <c r="D3" s="2">
-        <v>1636</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
@@ -645,13 +629,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>532</v>
+        <v>689</v>
       </c>
       <c r="C4" s="2">
         <v>0</v>
       </c>
       <c r="D4" s="2">
-        <v>532</v>
+        <v>689</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -659,21 +643,21 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>501</v>
+        <v>602</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>502</v>
+        <v>602</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2">
         <v>0</v>
@@ -687,7 +671,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2">
         <v>0</v>
@@ -698,7 +682,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2">
         <v>492</v>
@@ -712,7 +696,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B9" s="2">
         <v>490</v>
@@ -726,7 +710,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2">
         <v>357</v>
@@ -740,136 +724,136 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>37</v>
+        <v>7</v>
+      </c>
+      <c r="B11" s="2">
+        <v>266</v>
       </c>
       <c r="C11" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2">
-        <v>300</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B12" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C12" s="2">
         <v>0</v>
       </c>
       <c r="D12" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2">
-        <v>217</v>
+        <v>236</v>
       </c>
       <c r="C13" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2">
-        <v>219</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
+      </c>
+      <c r="B14" s="2">
+        <v>217</v>
       </c>
       <c r="C14" s="2">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>138</v>
+      <c r="B15" s="2">
+        <v>73</v>
+      </c>
+      <c r="C15" s="2">
+        <v>83</v>
+      </c>
+      <c r="D15" s="2">
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="4">
-        <v>122</v>
-      </c>
-      <c r="C16" s="4">
-        <v>0</v>
-      </c>
-      <c r="D16" s="4">
-        <v>122</v>
+      <c r="A16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="2">
+        <v>148</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2">
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="2">
-        <v>117</v>
+        <v>45</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>33</v>
       </c>
       <c r="C17" s="2">
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>117</v>
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="2">
-        <v>0</v>
-      </c>
-      <c r="D18" s="2">
-        <v>100</v>
+      <c r="A18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="4">
+        <v>122</v>
+      </c>
+      <c r="C18" s="4">
+        <v>0</v>
+      </c>
+      <c r="D18" s="4">
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>40</v>
+        <v>9</v>
+      </c>
+      <c r="B19" s="2">
+        <v>117</v>
       </c>
       <c r="C19" s="2">
         <v>0</v>
       </c>
       <c r="D19" s="2">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>10</v>
+      </c>
+      <c r="B20" s="2">
+        <v>68</v>
       </c>
       <c r="C20" s="2">
         <v>0</v>
@@ -880,108 +864,108 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B21" s="2">
-        <v>84</v>
+        <v>183</v>
       </c>
       <c r="C21" s="2">
         <v>0</v>
       </c>
       <c r="D21" s="2">
-        <v>84</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B22" s="2">
-        <v>83</v>
+        <v>173</v>
       </c>
       <c r="C22" s="2">
         <v>0</v>
       </c>
       <c r="D22" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C23" s="2">
         <v>0</v>
       </c>
       <c r="D23" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C24" s="2">
         <v>0</v>
       </c>
       <c r="D24" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>18</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>41</v>
+        <v>14</v>
+      </c>
+      <c r="B25" s="2">
+        <v>72</v>
       </c>
       <c r="C25" s="2">
         <v>0</v>
       </c>
       <c r="D25" s="2">
-        <v>57</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="2">
-        <v>54</v>
+        <v>15</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="C26" s="2">
         <v>0</v>
       </c>
       <c r="D26" s="2">
-        <v>54</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="2" t="s">
         <v>42</v>
       </c>
+      <c r="B27" s="2">
+        <v>54</v>
+      </c>
       <c r="C27" s="2">
         <v>0</v>
       </c>
       <c r="D27" s="2">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C28" s="2">
         <v>0</v>
@@ -992,10 +976,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C29" s="2">
         <v>0</v>
@@ -1006,10 +990,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C30" s="2">
         <v>0</v>
@@ -1020,66 +1004,66 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="B31" s="2">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="C31" s="2">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="D31" s="2">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B32" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
       </c>
       <c r="D32" s="2">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>44</v>
+        <v>18</v>
+      </c>
+      <c r="B33" s="2">
+        <v>29</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
       </c>
       <c r="D33" s="2">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>25</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>44</v>
+        <v>19</v>
+      </c>
+      <c r="B34" s="2">
+        <v>23</v>
       </c>
       <c r="C34" s="2">
         <v>0</v>
       </c>
       <c r="D34" s="2">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C35" s="2">
         <v>0</v>
@@ -1090,63 +1074,63 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="2">
-        <v>19</v>
+        <v>44</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="C36" s="2">
         <v>0</v>
       </c>
       <c r="D36" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B37" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C37" s="2">
         <v>0</v>
       </c>
       <c r="D37" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B38" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C38" s="2">
         <v>0</v>
       </c>
       <c r="D38" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B39" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C39" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D39" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B40" s="2">
         <v>0</v>
@@ -1160,21 +1144,21 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B41" s="2">
         <v>0</v>
       </c>
       <c r="C41" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D41" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B42" s="2">
         <v>0</v>
@@ -1188,7 +1172,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B43" s="2">
         <v>0</v>
@@ -1202,21 +1186,21 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B44" s="2">
         <v>0</v>
       </c>
       <c r="C44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B45" s="2">
         <v>0</v>
@@ -1230,33 +1214,22 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B46" s="2">
         <v>0</v>
       </c>
       <c r="C46" s="2">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="D46" s="2">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" s="2">
-        <v>0</v>
-      </c>
-      <c r="C47" s="2">
-        <v>83</v>
-      </c>
-      <c r="D47" s="2">
-        <v>83</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D46">
+    <sortCondition descending="1" ref="D2:D46"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/Museum leaderboard.xlsx
+++ b/data/Museum leaderboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brinda/Documents/MRes project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE11C40-0492-DD45-ADFB-D89E3579E890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38AAC66-7E9B-E74F-A32C-91BD15CF611D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
